--- a/research/traditional_assets/database/data/colombia/colombia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09320000000000001</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0358</v>
+        <v>0.015</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>87.3</v>
+        <v>45.2</v>
       </c>
       <c r="L2">
-        <v>0.1920369555653322</v>
+        <v>0.1305603697284806</v>
       </c>
       <c r="M2">
-        <v>30.7</v>
+        <v>25.5</v>
       </c>
       <c r="N2">
-        <v>0.05302245250431779</v>
+        <v>0.0728363324764353</v>
       </c>
       <c r="O2">
-        <v>0.3516609392898053</v>
+        <v>0.5641592920353982</v>
       </c>
       <c r="P2">
-        <v>30.7</v>
+        <v>25.5</v>
       </c>
       <c r="Q2">
-        <v>0.05302245250431779</v>
+        <v>0.0728363324764353</v>
       </c>
       <c r="R2">
-        <v>0.3516609392898053</v>
+        <v>0.5641592920353982</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>123.3</v>
+        <v>504.4</v>
       </c>
       <c r="V2">
-        <v>0.2129533678756477</v>
+        <v>1.440731219651528</v>
       </c>
       <c r="W2">
-        <v>0.1091386423302913</v>
+        <v>0.05243011251594943</v>
       </c>
       <c r="X2">
-        <v>0.09270893380951198</v>
+        <v>0.1253618259031971</v>
       </c>
       <c r="Y2">
-        <v>0.01642970852077931</v>
+        <v>-0.07293171338724763</v>
       </c>
       <c r="Z2">
-        <v>0.3314619030258841</v>
+        <v>0.2220654265554843</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05435764928711172</v>
+        <v>0.0688372834824498</v>
       </c>
       <c r="AC2">
-        <v>-0.05435764928711172</v>
+        <v>-0.0688372834824498</v>
       </c>
       <c r="AD2">
-        <v>820.2</v>
+        <v>862.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>820.2</v>
+        <v>862.3</v>
       </c>
       <c r="AG2">
-        <v>696.9000000000001</v>
+        <v>357.9</v>
       </c>
       <c r="AH2">
-        <v>0.5861921097770154</v>
+        <v>0.7112339161992741</v>
       </c>
       <c r="AI2">
-        <v>0.4850958126330731</v>
+        <v>0.5481533278240417</v>
       </c>
       <c r="AJ2">
-        <v>0.5462026804608512</v>
+        <v>0.5055084745762711</v>
       </c>
       <c r="AK2">
-        <v>0.4445933014354068</v>
+        <v>0.3348928604847011</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09320000000000001</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0358</v>
+        <v>0.015</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>87.3</v>
+        <v>45.2</v>
       </c>
       <c r="L3">
-        <v>0.1920369555653322</v>
+        <v>0.1305603697284806</v>
       </c>
       <c r="M3">
-        <v>30.7</v>
+        <v>25.5</v>
       </c>
       <c r="N3">
-        <v>0.05302245250431779</v>
+        <v>0.0728363324764353</v>
       </c>
       <c r="O3">
-        <v>0.3516609392898053</v>
+        <v>0.5641592920353982</v>
       </c>
       <c r="P3">
-        <v>30.7</v>
+        <v>25.5</v>
       </c>
       <c r="Q3">
-        <v>0.05302245250431779</v>
+        <v>0.0728363324764353</v>
       </c>
       <c r="R3">
-        <v>0.3516609392898053</v>
+        <v>0.5641592920353982</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>123.3</v>
+        <v>504.4</v>
       </c>
       <c r="V3">
-        <v>0.2129533678756477</v>
+        <v>1.440731219651528</v>
       </c>
       <c r="W3">
-        <v>0.1091386423302913</v>
+        <v>0.05243011251594943</v>
       </c>
       <c r="X3">
-        <v>0.09270893380951198</v>
+        <v>0.1253618259031971</v>
       </c>
       <c r="Y3">
-        <v>0.01642970852077931</v>
+        <v>-0.07293171338724763</v>
       </c>
       <c r="Z3">
-        <v>0.3314619030258841</v>
+        <v>0.2220654265554843</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05435764928711172</v>
+        <v>0.0688372834824498</v>
       </c>
       <c r="AC3">
-        <v>-0.05435764928711172</v>
+        <v>-0.0688372834824498</v>
       </c>
       <c r="AD3">
-        <v>820.2</v>
+        <v>862.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>820.2</v>
+        <v>862.3</v>
       </c>
       <c r="AG3">
-        <v>696.9000000000001</v>
+        <v>357.9</v>
       </c>
       <c r="AH3">
-        <v>0.5861921097770154</v>
+        <v>0.7112339161992741</v>
       </c>
       <c r="AI3">
-        <v>0.4850958126330731</v>
+        <v>0.5481533278240417</v>
       </c>
       <c r="AJ3">
-        <v>0.5462026804608512</v>
+        <v>0.5055084745762711</v>
       </c>
       <c r="AK3">
-        <v>0.4445933014354068</v>
+        <v>0.3348928604847011</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/colombia/colombia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_banks_regional.xlsx
@@ -588,10 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05230000000000001</v>
-      </c>
-      <c r="E2">
-        <v>0.015</v>
+        <v>-0.127</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +603,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>45.2</v>
+        <v>-97.5</v>
       </c>
       <c r="L2">
-        <v>0.1305603697284806</v>
+        <v>-0.5584192439862543</v>
       </c>
       <c r="M2">
-        <v>25.5</v>
+        <v>16.4</v>
       </c>
       <c r="N2">
-        <v>0.0728363324764353</v>
+        <v>0.03697024346257889</v>
       </c>
       <c r="O2">
-        <v>0.5641592920353982</v>
+        <v>-0.1682051282051282</v>
       </c>
       <c r="P2">
-        <v>25.5</v>
+        <v>16.4</v>
       </c>
       <c r="Q2">
-        <v>0.0728363324764353</v>
+        <v>0.03697024346257889</v>
       </c>
       <c r="R2">
-        <v>0.5641592920353982</v>
+        <v>-0.1682051282051282</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>504.4</v>
+        <v>545.3</v>
       </c>
       <c r="V2">
-        <v>1.440731219651528</v>
+        <v>1.229260595130748</v>
       </c>
       <c r="W2">
-        <v>0.05243011251594943</v>
+        <v>-0.1383763837638376</v>
       </c>
       <c r="X2">
-        <v>0.1253618259031971</v>
+        <v>0.08580011705364571</v>
       </c>
       <c r="Y2">
-        <v>-0.07293171338724763</v>
+        <v>-0.2241765008174833</v>
       </c>
       <c r="Z2">
-        <v>0.2220654265554843</v>
+        <v>0.1643294117647059</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0688372834824498</v>
+        <v>0.05809363385368052</v>
       </c>
       <c r="AC2">
-        <v>-0.0688372834824498</v>
+        <v>-0.05809363385368052</v>
       </c>
       <c r="AD2">
-        <v>862.3</v>
+        <v>801.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>862.3</v>
+        <v>801.6</v>
       </c>
       <c r="AG2">
-        <v>357.9</v>
+        <v>256.3000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.7112339161992741</v>
+        <v>0.6437520077096048</v>
       </c>
       <c r="AI2">
-        <v>0.5481533278240417</v>
+        <v>0.5231351563009854</v>
       </c>
       <c r="AJ2">
-        <v>0.5055084745762711</v>
+        <v>0.366195170738677</v>
       </c>
       <c r="AK2">
-        <v>0.3348928604847011</v>
+        <v>0.2596757852077001</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +707,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05230000000000001</v>
-      </c>
-      <c r="E3">
-        <v>0.015</v>
+        <v>-0.127</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +722,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>45.2</v>
+        <v>-97.5</v>
       </c>
       <c r="L3">
-        <v>0.1305603697284806</v>
+        <v>-0.5584192439862543</v>
       </c>
       <c r="M3">
-        <v>25.5</v>
+        <v>16.4</v>
       </c>
       <c r="N3">
-        <v>0.0728363324764353</v>
+        <v>0.03697024346257889</v>
       </c>
       <c r="O3">
-        <v>0.5641592920353982</v>
+        <v>-0.1682051282051282</v>
       </c>
       <c r="P3">
-        <v>25.5</v>
+        <v>16.4</v>
       </c>
       <c r="Q3">
-        <v>0.0728363324764353</v>
+        <v>0.03697024346257889</v>
       </c>
       <c r="R3">
-        <v>0.5641592920353982</v>
+        <v>-0.1682051282051282</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>504.4</v>
+        <v>545.3</v>
       </c>
       <c r="V3">
-        <v>1.440731219651528</v>
+        <v>1.229260595130748</v>
       </c>
       <c r="W3">
-        <v>0.05243011251594943</v>
+        <v>-0.1383763837638376</v>
       </c>
       <c r="X3">
-        <v>0.1253618259031971</v>
+        <v>0.08580011705364571</v>
       </c>
       <c r="Y3">
-        <v>-0.07293171338724763</v>
+        <v>-0.2241765008174833</v>
       </c>
       <c r="Z3">
-        <v>0.2220654265554843</v>
+        <v>0.1643294117647059</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0688372834824498</v>
+        <v>0.05809363385368052</v>
       </c>
       <c r="AC3">
-        <v>-0.0688372834824498</v>
+        <v>-0.05809363385368052</v>
       </c>
       <c r="AD3">
-        <v>862.3</v>
+        <v>801.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>862.3</v>
+        <v>801.6</v>
       </c>
       <c r="AG3">
-        <v>357.9</v>
+        <v>256.3000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.7112339161992741</v>
+        <v>0.6437520077096048</v>
       </c>
       <c r="AI3">
-        <v>0.5481533278240417</v>
+        <v>0.5231351563009854</v>
       </c>
       <c r="AJ3">
-        <v>0.5055084745762711</v>
+        <v>0.366195170738677</v>
       </c>
       <c r="AK3">
-        <v>0.3348928604847011</v>
+        <v>0.2596757852077001</v>
       </c>
       <c r="AL3">
         <v>0</v>
